--- a/source/時刻データ.xlsx
+++ b/source/時刻データ.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0161A34C-6470-46EB-ABAD-B6D8935753FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -2352,16 +2352,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AM70"/>
-  <sheetFormatPr defaultColWidth="8.375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.3984375" defaultRowHeight="15.9" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="3.375" style="45" customWidth="1"/>
-    <col min="3" max="37" width="10.625" style="2" customWidth="1"/>
-    <col min="38" max="38" width="8.375" style="1" customWidth="1"/>
-    <col min="39" max="16384" width="8.375" style="1"/>
+    <col min="1" max="1" width="7.09765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="3.3984375" style="45" customWidth="1"/>
+    <col min="3" max="37" width="10.59765625" style="2" customWidth="1"/>
+    <col min="38" max="38" width="8.3984375" style="1" customWidth="1"/>
+    <col min="39" max="16384" width="8.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="124" t="s">
         <v>0</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:37" s="5" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:37" s="5" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="97"/>
       <c r="B2" s="98"/>
       <c r="C2" s="99"/>
@@ -2471,7 +2471,7 @@
       <c r="AJ2" s="103"/>
       <c r="AK2" s="104"/>
     </row>
-    <row r="3" spans="1:37" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:37" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="37" t="s">
         <v>15</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="41" t="s">
         <v>18</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="41" t="s">
         <v>100</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="41" t="s">
         <v>19</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="111"/>
       <c r="B7" s="141"/>
       <c r="C7" s="142" t="s">
@@ -2998,7 +2998,7 @@
       <c r="AJ7" s="148"/>
       <c r="AK7" s="149"/>
     </row>
-    <row r="8" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="150" t="s">
         <v>37</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="58" t="s">
         <v>38</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="57" t="s">
         <v>40</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="136" t="s">
         <v>99</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="57" t="s">
         <v>41</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="156" t="s">
         <v>42</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="150" t="s">
         <v>42</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="135" t="s">
         <v>43</v>
       </c>
@@ -3902,7 +3902,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="57" t="s">
         <v>44</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="57" t="s">
         <v>45</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="156" t="s">
         <v>46</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="150" t="s">
         <v>46</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="57" t="s">
         <v>47</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="136" t="s">
         <v>101</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="57" t="s">
         <v>48</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="156" t="s">
         <v>49</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="39" t="s">
         <v>49</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="41" t="s">
         <v>50</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="41" t="s">
         <v>52</v>
       </c>
@@ -5145,7 +5145,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="41" t="s">
         <v>53</v>
       </c>
@@ -5258,7 +5258,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="56" t="s">
         <v>54</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="41" t="s">
         <v>55</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="56" t="s">
         <v>56</v>
       </c>
@@ -5597,7 +5597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="38" t="s">
         <v>57</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:37" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A32" s="85"/>
       <c r="B32" s="86"/>
       <c r="C32" s="87"/>
@@ -5749,7 +5749,7 @@
       <c r="AJ32" s="87"/>
       <c r="AK32" s="90"/>
     </row>
-    <row r="33" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="113" t="s">
         <v>58</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:37" s="3" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:37" s="3" customFormat="1" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="12"/>
       <c r="B34" s="53"/>
       <c r="C34" s="10"/>
@@ -5859,7 +5859,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="37" t="s">
         <v>73</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="56" t="s">
         <v>56</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="41" t="s">
         <v>102</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>0.85833333333333328</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="56" t="s">
         <v>54</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>0.87291666666666667</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="41" t="s">
         <v>53</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>0.88402777777777775</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="41" t="s">
         <v>52</v>
       </c>
@@ -6537,7 +6537,7 @@
         <v>0.90208333333333335</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="41" t="s">
         <v>74</v>
       </c>
@@ -6650,7 +6650,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="40" t="s">
         <v>49</v>
       </c>
@@ -6763,7 +6763,7 @@
         <v>0.91805555555555551</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:37" ht="18.600000000000001" x14ac:dyDescent="0.45">
       <c r="A43" s="111"/>
       <c r="B43" s="110"/>
       <c r="C43" s="109" t="s">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AK43" s="106"/>
     </row>
-    <row r="44" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="42" t="s">
         <v>49</v>
       </c>
@@ -6953,7 +6953,7 @@
         <v>0.91874999999999996</v>
       </c>
     </row>
-    <row r="45" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="57" t="s">
         <v>48</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="136" t="s">
         <v>101</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="57" t="s">
         <v>47</v>
       </c>
@@ -7292,7 +7292,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="156" t="s">
         <v>46</v>
       </c>
@@ -7405,7 +7405,7 @@
         <v>0.92638888888888893</v>
       </c>
     </row>
-    <row r="49" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="150" t="s">
         <v>46</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>0.92638888888888893</v>
       </c>
     </row>
-    <row r="50" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="57" t="s">
         <v>45</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="57" t="s">
         <v>44</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="57" t="s">
         <v>43</v>
       </c>
@@ -7857,7 +7857,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="156" t="s">
         <v>42</v>
       </c>
@@ -7970,7 +7970,7 @@
         <v>0.93472222222222223</v>
       </c>
     </row>
-    <row r="54" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="150" t="s">
         <v>42</v>
       </c>
@@ -8083,7 +8083,7 @@
         <v>0.93472222222222223</v>
       </c>
     </row>
-    <row r="55" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="57" t="s">
         <v>41</v>
       </c>
@@ -8196,7 +8196,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="136" t="s">
         <v>99</v>
       </c>
@@ -8309,7 +8309,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="57" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="57" t="s">
         <v>40</v>
       </c>
@@ -8422,7 +8422,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:37" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="59" t="s">
         <v>38</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="156" t="s">
         <v>19</v>
       </c>
@@ -8648,7 +8648,7 @@
         <v>0.94513888888888886</v>
       </c>
     </row>
-    <row r="60" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="43"/>
       <c r="B60" s="55"/>
       <c r="C60" s="6"/>
@@ -8691,7 +8691,7 @@
       <c r="AJ60" s="9"/>
       <c r="AK60" s="76"/>
     </row>
-    <row r="61" spans="1:37" s="13" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:37" s="13" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="39" t="s">
         <v>37</v>
       </c>
@@ -8804,7 +8804,7 @@
         <v>0.94652777777777775</v>
       </c>
     </row>
-    <row r="62" spans="1:37" s="13" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:37" s="13" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="40" t="s">
         <v>94</v>
       </c>
@@ -8917,7 +8917,7 @@
         <v>0.95972222222222225</v>
       </c>
     </row>
-    <row r="63" spans="1:37" s="13" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:37" s="13" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="40" t="s">
         <v>95</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>0.96597222222222223</v>
       </c>
     </row>
-    <row r="64" spans="1:37" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:37" s="13" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="44" t="s">
         <v>15</v>
       </c>
@@ -9143,7 +9143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:39" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:39" ht="9.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A65" s="91"/>
       <c r="B65" s="92"/>
       <c r="C65" s="93"/>
@@ -9182,13 +9182,13 @@
       <c r="AJ65" s="93"/>
       <c r="AK65" s="96"/>
     </row>
-    <row r="68" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:39" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="1"/>
       <c r="B68" s="61"/>
       <c r="C68" s="45"/>
       <c r="AL68" s="2"/>
     </row>
-    <row r="69" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:39" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="61"/>
@@ -9196,7 +9196,7 @@
       <c r="AL69" s="2"/>
       <c r="AM69" s="2"/>
     </row>
-    <row r="70" spans="1:39" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:39" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="1"/>
       <c r="B70" s="4"/>
       <c r="C70" s="45"/>
